--- a/docs/phase-0.5-review.xlsx
+++ b/docs/phase-0.5-review.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用說明" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -33,47 +33,47 @@
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <b val="1"/>
-      <color rgb="FF157554"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
       <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF157554"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -115,74 +115,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -266,6 +247,41 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pacevera</author>
+  </authors>
+  <commentList>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>用白話詢問，不使用『抑制候選』或『仲裁』這類工程術語。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pacevera</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>例如：原本的 Keep 方案沒有被採用，因為降低強度的規則優先。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>確認審查者知道：當規則衝突時，哪條規則優先並決定最後結果。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,214 +582,190 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Pacevera Phase 0.5 審查工作簿</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>確認審查者是否能理解排定課表、Decision Graph，以及僅供原型使用的 Outcome 回報控制項。</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>使用方式</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>1. 開啟 docs/pacevera-home.html，不先解釋介面。</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2. 請審查者完成下方三項任務。</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>3. 在「審查紀錄」工作表中，每位審查者填寫一列。</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>4. 不要記錄姓名、電子郵件、provider token 或真實健康資料。</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>5. 使用「摘要」工作表檢查 4/5 成功門檻。</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="23" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>審查任務</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>決策理解</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>原本排定什麼？今天應該做什麼？</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="D15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Decision Trace 理解</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>為什麼改變？哪條規則主導，哪條規則被抑制？</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>為什麼改變？哪個方案沒有採用？哪條規則優先？</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Outcome 理解</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>你會如何回報 Adopted、Changed、Skipped 與主觀感受強度？</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>成功門檻</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>至少 5 位審查者中的 4 位，應能在沒有提示下完成核心任務。任何隱私理解錯誤都會阻擋發布。</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -787,6 +779,7 @@
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -802,458 +795,457 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19.3984375" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="7"/>
+    <col width="19.3984375" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="10"/>
     <col width="18" customWidth="1" min="11" max="12"/>
     <col width="38" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="30.796875" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+    <row r="1" ht="42" customFormat="1" customHeight="1" s="14">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>審查者 ID</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>找到 from → to</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>說出變更</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>找到 Trace</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>理解觸發規則</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
-        <is>
-          <t>理解被抑制候選</t>
-        </is>
-      </c>
-      <c r="I1" s="17" t="inlineStr">
-        <is>
-          <t>理解仲裁</t>
-        </is>
-      </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>理解未採用的其他方案</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>理解哪條規則優先</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>理解來源追溯</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>理解 Outcome</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>理解未儲存</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>困惑／觀察</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>最有用的元素</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="13" t="inlineStr">
         <is>
           <t>一項建議變更</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>保留／修改／移除</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="18" t="n"/>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
-      <c r="J2" s="18" t="n"/>
-      <c r="K2" s="18" t="n"/>
-      <c r="L2" s="18" t="n"/>
-      <c r="M2" s="18" t="n"/>
-      <c r="N2" s="18" t="n"/>
-      <c r="O2" s="18" t="n"/>
-      <c r="P2" s="18" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="20" t="n"/>
-      <c r="K3" s="20" t="n"/>
-      <c r="L3" s="20" t="n"/>
-      <c r="M3" s="20" t="n"/>
-      <c r="N3" s="20" t="n"/>
-      <c r="O3" s="20" t="n"/>
-      <c r="P3" s="20" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
-      <c r="H4" s="18" t="n"/>
-      <c r="I4" s="18" t="n"/>
-      <c r="J4" s="18" t="n"/>
-      <c r="K4" s="18" t="n"/>
-      <c r="L4" s="18" t="n"/>
-      <c r="M4" s="18" t="n"/>
-      <c r="N4" s="18" t="n"/>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="n"/>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="20" t="n"/>
-      <c r="L5" s="20" t="n"/>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="20" t="n"/>
-      <c r="O5" s="20" t="n"/>
-      <c r="P5" s="20" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="19" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
-      <c r="O6" s="18" t="n"/>
-      <c r="P6" s="18" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="18" t="n"/>
-      <c r="P8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-      <c r="P9" s="20" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="18" t="n"/>
-      <c r="N10" s="18" t="n"/>
-      <c r="O10" s="18" t="n"/>
-      <c r="P10" s="18" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
-      <c r="P11" s="20" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-      <c r="P12" s="18" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="20" t="n"/>
-      <c r="P13" s="20" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="18" t="n"/>
-      <c r="O14" s="18" t="n"/>
-      <c r="P14" s="18" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="20" t="n"/>
-      <c r="O15" s="20" t="n"/>
-      <c r="P15" s="20" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-      <c r="P16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n"/>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="20" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="n"/>
-      <c r="I18" s="18" t="n"/>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="18" t="n"/>
-      <c r="M18" s="18" t="n"/>
-      <c r="N18" s="18" t="n"/>
-      <c r="O18" s="18" t="n"/>
-      <c r="P18" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
-      <c r="I20" s="18" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="18" t="n"/>
-      <c r="O20" s="18" t="n"/>
-      <c r="P20" s="18" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="20" t="n"/>
-      <c r="P21" s="20" t="n"/>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="12" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="12" t="n"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="12" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P21"/>
@@ -1274,6 +1266,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1287,181 +1280,181 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="30.59765625" customWidth="1" min="2" max="2"/>
+    <col width="63" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Phase 0.5 Review Summary</t>
         </is>
       </c>
-      <c r="B1" s="20" t="n"/>
-      <c r="C1" s="20" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="B1" s="17" t="n"/>
+      <c r="C1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="39" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>目標／解讀</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="4" ht="39" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>已填寫審查者數</t>
         </is>
       </c>
-      <c r="B4" s="20">
-        <f>COUNTA('審查紀錄'!A2:A21)</f>
+      <c r="B4" s="12">
+        <f>COUNTA(審查紀錄!A2:A21)</f>
         <v/>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>目標：5</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>找到 from → to</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>COUNTIF('審查紀錄'!D2:D21,"是")</f>
+      <c r="B5" s="12">
+        <f>COUNTIF(審查紀錄!D2:D21,"是")</f>
         <v/>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>目標：≥4</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="39" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>找到 Decision Trace</t>
         </is>
       </c>
-      <c r="B6" s="20">
-        <f>COUNTIF('審查紀錄'!F2:F21,"是")</f>
+      <c r="B6" s="12">
+        <f>COUNTIF(審查紀錄!F2:F21,"是")</f>
         <v/>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>目標：≥4</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="39" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>理解仲裁</t>
         </is>
       </c>
-      <c r="B7" s="20">
-        <f>COUNTIF('審查紀錄'!I2:I21,"是")</f>
+      <c r="B7" s="12">
+        <f>COUNTIF(審查紀錄!I2:I21,"是")</f>
         <v/>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>目標：≥4</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>理解來源追溯</t>
         </is>
       </c>
-      <c r="B8" s="20">
-        <f>COUNTIF('審查紀錄'!J2:J21,"是")</f>
+      <c r="B8" s="12">
+        <f>COUNTIF(審查紀錄!J2:J21,"是")</f>
         <v/>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>目標：≥4</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>理解未儲存</t>
         </is>
       </c>
-      <c r="B9" s="20">
-        <f>COUNTIF('審查紀錄'!L2:L21,"是")</f>
+      <c r="B9" s="12">
+        <f>COUNTIF(審查紀錄!L2:L21,"是")</f>
         <v/>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>必須 ≥4；隱私理解錯誤會阻擋發布</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>審查狀態</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="12">
         <f>IF(B4=0,"尚未開始",IF(AND(B5&gt;=4,B6&gt;=4,B7&gt;=4,B8&gt;=4,B9&gt;=4),"通過理解門檻","需要審查／修訂"))</f>
         <v/>
       </c>
-      <c r="C12" s="20" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="C12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="31" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>重要提醒</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>本工作簿只記錄產品理解程度，不得包含健康資料、帳號識別資訊、OAuth token 或 provider 原始匯出檔。</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/phase-0.5-review.xlsx
+++ b/docs/phase-0.5-review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henryyeh/dev/fitness-mcp/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CEEA9C-5564-E449-AF53-9B05C75589B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82E2F1A-41A9-004A-8D3F-52BCC17BD6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用說明" sheetId="1" r:id="rId1"/>
